--- a/tools/candidates/p3-subject-remediation-20261014/unit-c-xlsx02-06/candidate/06-zhurnal-peredachi.xlsx
+++ b/tools/candidates/p3-subject-remediation-20261014/unit-c-xlsx02-06/candidate/06-zhurnal-peredachi.xlsx
@@ -99,7 +99,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="0.##"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -163,7 +163,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEFE7D2"/>
-        <bgColor rgb="FFFCE8E6"/>
+        <bgColor rgb="FFD9DDE3"/>
       </patternFill>
     </fill>
     <fill>
@@ -303,7 +303,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -314,7 +314,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFCE8E6"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -325,7 +325,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -361,7 +361,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFEFE7D2"/>
       <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -376,13 +376,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFFCE8E6"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFEFE7D2"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFC6EFCE"/>
+      <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -683,7 +683,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5" t="str">
-        <f aca="false">IF(COUNTA(B5:K5)=0,"",IF(OR(NOT(ISNUMBER(B5)),C5="",D5="",E5="",F5="",G5&lt;1,H5="",I5=""),"ЗАПОЛНИТЬ",IF(I5="Принято","ЗАКРЫТО",IF(I5="Возврат",IF(OR(NOT(ISNUMBER(J5)),J5&lt;B5,K5=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I5="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B5:K5)=0,"",IF(OR(NOT(ISNUMBER(B5)),B5&lt;DATE(2000,1,1),B5&gt;TODAY(),C5="",D5="",E5="",F5="",NOT(AND(ISNUMBER(G5),G5=INT(G5),G5&gt;=1,G5&lt;=10000)),NOT(OR(H5="Подпись на экземпляре",H5="ЭДО",H5="Письмо / курьер",H5="Иное подтверждение")),NOT(OR(I5="На проверке",I5="Принято",I5="Возврат"))),"ЗАПОЛНИТЬ",IF(I5="Принято","ЗАКРЫТО",IF(I5="Возврат",IF(OR(NOT(ISNUMBER(J5)),J5&lt;B5,J5&gt;TODAY(),K5=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -702,7 +702,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="str">
-        <f aca="false">IF(COUNTA(B6:K6)=0,"",IF(OR(NOT(ISNUMBER(B6)),C6="",D6="",E6="",F6="",G6&lt;1,H6="",I6=""),"ЗАПОЛНИТЬ",IF(I6="Принято","ЗАКРЫТО",IF(I6="Возврат",IF(OR(NOT(ISNUMBER(J6)),J6&lt;B6,K6=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I6="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B6:K6)=0,"",IF(OR(NOT(ISNUMBER(B6)),B6&lt;DATE(2000,1,1),B6&gt;TODAY(),C6="",D6="",E6="",F6="",NOT(AND(ISNUMBER(G6),G6=INT(G6),G6&gt;=1,G6&lt;=10000)),NOT(OR(H6="Подпись на экземпляре",H6="ЭДО",H6="Письмо / курьер",H6="Иное подтверждение")),NOT(OR(I6="На проверке",I6="Принято",I6="Возврат"))),"ЗАПОЛНИТЬ",IF(I6="Принято","ЗАКРЫТО",IF(I6="Возврат",IF(OR(NOT(ISNUMBER(J6)),J6&lt;B6,J6&gt;TODAY(),K6=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -721,7 +721,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5" t="str">
-        <f aca="false">IF(COUNTA(B7:K7)=0,"",IF(OR(NOT(ISNUMBER(B7)),C7="",D7="",E7="",F7="",G7&lt;1,H7="",I7=""),"ЗАПОЛНИТЬ",IF(I7="Принято","ЗАКРЫТО",IF(I7="Возврат",IF(OR(NOT(ISNUMBER(J7)),J7&lt;B7,K7=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I7="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B7:K7)=0,"",IF(OR(NOT(ISNUMBER(B7)),B7&lt;DATE(2000,1,1),B7&gt;TODAY(),C7="",D7="",E7="",F7="",NOT(AND(ISNUMBER(G7),G7=INT(G7),G7&gt;=1,G7&lt;=10000)),NOT(OR(H7="Подпись на экземпляре",H7="ЭДО",H7="Письмо / курьер",H7="Иное подтверждение")),NOT(OR(I7="На проверке",I7="Принято",I7="Возврат"))),"ЗАПОЛНИТЬ",IF(I7="Принято","ЗАКРЫТО",IF(I7="Возврат",IF(OR(NOT(ISNUMBER(J7)),J7&lt;B7,J7&gt;TODAY(),K7=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -740,7 +740,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5" t="str">
-        <f aca="false">IF(COUNTA(B8:K8)=0,"",IF(OR(NOT(ISNUMBER(B8)),C8="",D8="",E8="",F8="",G8&lt;1,H8="",I8=""),"ЗАПОЛНИТЬ",IF(I8="Принято","ЗАКРЫТО",IF(I8="Возврат",IF(OR(NOT(ISNUMBER(J8)),J8&lt;B8,K8=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I8="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B8:K8)=0,"",IF(OR(NOT(ISNUMBER(B8)),B8&lt;DATE(2000,1,1),B8&gt;TODAY(),C8="",D8="",E8="",F8="",NOT(AND(ISNUMBER(G8),G8=INT(G8),G8&gt;=1,G8&lt;=10000)),NOT(OR(H8="Подпись на экземпляре",H8="ЭДО",H8="Письмо / курьер",H8="Иное подтверждение")),NOT(OR(I8="На проверке",I8="Принято",I8="Возврат"))),"ЗАПОЛНИТЬ",IF(I8="Принято","ЗАКРЫТО",IF(I8="Возврат",IF(OR(NOT(ISNUMBER(J8)),J8&lt;B8,J8&gt;TODAY(),K8=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -759,7 +759,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5" t="str">
-        <f aca="false">IF(COUNTA(B9:K9)=0,"",IF(OR(NOT(ISNUMBER(B9)),C9="",D9="",E9="",F9="",G9&lt;1,H9="",I9=""),"ЗАПОЛНИТЬ",IF(I9="Принято","ЗАКРЫТО",IF(I9="Возврат",IF(OR(NOT(ISNUMBER(J9)),J9&lt;B9,K9=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I9="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B9:K9)=0,"",IF(OR(NOT(ISNUMBER(B9)),B9&lt;DATE(2000,1,1),B9&gt;TODAY(),C9="",D9="",E9="",F9="",NOT(AND(ISNUMBER(G9),G9=INT(G9),G9&gt;=1,G9&lt;=10000)),NOT(OR(H9="Подпись на экземпляре",H9="ЭДО",H9="Письмо / курьер",H9="Иное подтверждение")),NOT(OR(I9="На проверке",I9="Принято",I9="Возврат"))),"ЗАПОЛНИТЬ",IF(I9="Принято","ЗАКРЫТО",IF(I9="Возврат",IF(OR(NOT(ISNUMBER(J9)),J9&lt;B9,J9&gt;TODAY(),K9=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -778,7 +778,7 @@
       <c r="J10" s="6"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5" t="str">
-        <f aca="false">IF(COUNTA(B10:K10)=0,"",IF(OR(NOT(ISNUMBER(B10)),C10="",D10="",E10="",F10="",G10&lt;1,H10="",I10=""),"ЗАПОЛНИТЬ",IF(I10="Принято","ЗАКРЫТО",IF(I10="Возврат",IF(OR(NOT(ISNUMBER(J10)),J10&lt;B10,K10=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I10="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B10:K10)=0,"",IF(OR(NOT(ISNUMBER(B10)),B10&lt;DATE(2000,1,1),B10&gt;TODAY(),C10="",D10="",E10="",F10="",NOT(AND(ISNUMBER(G10),G10=INT(G10),G10&gt;=1,G10&lt;=10000)),NOT(OR(H10="Подпись на экземпляре",H10="ЭДО",H10="Письмо / курьер",H10="Иное подтверждение")),NOT(OR(I10="На проверке",I10="Принято",I10="Возврат"))),"ЗАПОЛНИТЬ",IF(I10="Принято","ЗАКРЫТО",IF(I10="Возврат",IF(OR(NOT(ISNUMBER(J10)),J10&lt;B10,J10&gt;TODAY(),K10=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -797,7 +797,7 @@
       <c r="J11" s="6"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5" t="str">
-        <f aca="false">IF(COUNTA(B11:K11)=0,"",IF(OR(NOT(ISNUMBER(B11)),C11="",D11="",E11="",F11="",G11&lt;1,H11="",I11=""),"ЗАПОЛНИТЬ",IF(I11="Принято","ЗАКРЫТО",IF(I11="Возврат",IF(OR(NOT(ISNUMBER(J11)),J11&lt;B11,K11=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I11="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B11:K11)=0,"",IF(OR(NOT(ISNUMBER(B11)),B11&lt;DATE(2000,1,1),B11&gt;TODAY(),C11="",D11="",E11="",F11="",NOT(AND(ISNUMBER(G11),G11=INT(G11),G11&gt;=1,G11&lt;=10000)),NOT(OR(H11="Подпись на экземпляре",H11="ЭДО",H11="Письмо / курьер",H11="Иное подтверждение")),NOT(OR(I11="На проверке",I11="Принято",I11="Возврат"))),"ЗАПОЛНИТЬ",IF(I11="Принято","ЗАКРЫТО",IF(I11="Возврат",IF(OR(NOT(ISNUMBER(J11)),J11&lt;B11,J11&gt;TODAY(),K11=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -816,7 +816,7 @@
       <c r="J12" s="6"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5" t="str">
-        <f aca="false">IF(COUNTA(B12:K12)=0,"",IF(OR(NOT(ISNUMBER(B12)),C12="",D12="",E12="",F12="",G12&lt;1,H12="",I12=""),"ЗАПОЛНИТЬ",IF(I12="Принято","ЗАКРЫТО",IF(I12="Возврат",IF(OR(NOT(ISNUMBER(J12)),J12&lt;B12,K12=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I12="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B12:K12)=0,"",IF(OR(NOT(ISNUMBER(B12)),B12&lt;DATE(2000,1,1),B12&gt;TODAY(),C12="",D12="",E12="",F12="",NOT(AND(ISNUMBER(G12),G12=INT(G12),G12&gt;=1,G12&lt;=10000)),NOT(OR(H12="Подпись на экземпляре",H12="ЭДО",H12="Письмо / курьер",H12="Иное подтверждение")),NOT(OR(I12="На проверке",I12="Принято",I12="Возврат"))),"ЗАПОЛНИТЬ",IF(I12="Принято","ЗАКРЫТО",IF(I12="Возврат",IF(OR(NOT(ISNUMBER(J12)),J12&lt;B12,J12&gt;TODAY(),K12=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -835,7 +835,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5" t="str">
-        <f aca="false">IF(COUNTA(B13:K13)=0,"",IF(OR(NOT(ISNUMBER(B13)),C13="",D13="",E13="",F13="",G13&lt;1,H13="",I13=""),"ЗАПОЛНИТЬ",IF(I13="Принято","ЗАКРЫТО",IF(I13="Возврат",IF(OR(NOT(ISNUMBER(J13)),J13&lt;B13,K13=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I13="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B13:K13)=0,"",IF(OR(NOT(ISNUMBER(B13)),B13&lt;DATE(2000,1,1),B13&gt;TODAY(),C13="",D13="",E13="",F13="",NOT(AND(ISNUMBER(G13),G13=INT(G13),G13&gt;=1,G13&lt;=10000)),NOT(OR(H13="Подпись на экземпляре",H13="ЭДО",H13="Письмо / курьер",H13="Иное подтверждение")),NOT(OR(I13="На проверке",I13="Принято",I13="Возврат"))),"ЗАПОЛНИТЬ",IF(I13="Принято","ЗАКРЫТО",IF(I13="Возврат",IF(OR(NOT(ISNUMBER(J13)),J13&lt;B13,J13&gt;TODAY(),K13=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5" t="str">
-        <f aca="false">IF(COUNTA(B14:K14)=0,"",IF(OR(NOT(ISNUMBER(B14)),C14="",D14="",E14="",F14="",G14&lt;1,H14="",I14=""),"ЗАПОЛНИТЬ",IF(I14="Принято","ЗАКРЫТО",IF(I14="Возврат",IF(OR(NOT(ISNUMBER(J14)),J14&lt;B14,K14=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I14="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B14:K14)=0,"",IF(OR(NOT(ISNUMBER(B14)),B14&lt;DATE(2000,1,1),B14&gt;TODAY(),C14="",D14="",E14="",F14="",NOT(AND(ISNUMBER(G14),G14=INT(G14),G14&gt;=1,G14&lt;=10000)),NOT(OR(H14="Подпись на экземпляре",H14="ЭДО",H14="Письмо / курьер",H14="Иное подтверждение")),NOT(OR(I14="На проверке",I14="Принято",I14="Возврат"))),"ЗАПОЛНИТЬ",IF(I14="Принято","ЗАКРЫТО",IF(I14="Возврат",IF(OR(NOT(ISNUMBER(J14)),J14&lt;B14,J14&gt;TODAY(),K14=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -873,7 +873,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5" t="str">
-        <f aca="false">IF(COUNTA(B15:K15)=0,"",IF(OR(NOT(ISNUMBER(B15)),C15="",D15="",E15="",F15="",G15&lt;1,H15="",I15=""),"ЗАПОЛНИТЬ",IF(I15="Принято","ЗАКРЫТО",IF(I15="Возврат",IF(OR(NOT(ISNUMBER(J15)),J15&lt;B15,K15=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I15="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B15:K15)=0,"",IF(OR(NOT(ISNUMBER(B15)),B15&lt;DATE(2000,1,1),B15&gt;TODAY(),C15="",D15="",E15="",F15="",NOT(AND(ISNUMBER(G15),G15=INT(G15),G15&gt;=1,G15&lt;=10000)),NOT(OR(H15="Подпись на экземпляре",H15="ЭДО",H15="Письмо / курьер",H15="Иное подтверждение")),NOT(OR(I15="На проверке",I15="Принято",I15="Возврат"))),"ЗАПОЛНИТЬ",IF(I15="Принято","ЗАКРЫТО",IF(I15="Возврат",IF(OR(NOT(ISNUMBER(J15)),J15&lt;B15,J15&gt;TODAY(),K15=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -892,7 +892,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5" t="str">
-        <f aca="false">IF(COUNTA(B16:K16)=0,"",IF(OR(NOT(ISNUMBER(B16)),C16="",D16="",E16="",F16="",G16&lt;1,H16="",I16=""),"ЗАПОЛНИТЬ",IF(I16="Принято","ЗАКРЫТО",IF(I16="Возврат",IF(OR(NOT(ISNUMBER(J16)),J16&lt;B16,K16=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I16="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B16:K16)=0,"",IF(OR(NOT(ISNUMBER(B16)),B16&lt;DATE(2000,1,1),B16&gt;TODAY(),C16="",D16="",E16="",F16="",NOT(AND(ISNUMBER(G16),G16=INT(G16),G16&gt;=1,G16&lt;=10000)),NOT(OR(H16="Подпись на экземпляре",H16="ЭДО",H16="Письмо / курьер",H16="Иное подтверждение")),NOT(OR(I16="На проверке",I16="Принято",I16="Возврат"))),"ЗАПОЛНИТЬ",IF(I16="Принято","ЗАКРЫТО",IF(I16="Возврат",IF(OR(NOT(ISNUMBER(J16)),J16&lt;B16,J16&gt;TODAY(),K16=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -911,7 +911,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5" t="str">
-        <f aca="false">IF(COUNTA(B17:K17)=0,"",IF(OR(NOT(ISNUMBER(B17)),C17="",D17="",E17="",F17="",G17&lt;1,H17="",I17=""),"ЗАПОЛНИТЬ",IF(I17="Принято","ЗАКРЫТО",IF(I17="Возврат",IF(OR(NOT(ISNUMBER(J17)),J17&lt;B17,K17=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I17="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B17:K17)=0,"",IF(OR(NOT(ISNUMBER(B17)),B17&lt;DATE(2000,1,1),B17&gt;TODAY(),C17="",D17="",E17="",F17="",NOT(AND(ISNUMBER(G17),G17=INT(G17),G17&gt;=1,G17&lt;=10000)),NOT(OR(H17="Подпись на экземпляре",H17="ЭДО",H17="Письмо / курьер",H17="Иное подтверждение")),NOT(OR(I17="На проверке",I17="Принято",I17="Возврат"))),"ЗАПОЛНИТЬ",IF(I17="Принято","ЗАКРЫТО",IF(I17="Возврат",IF(OR(NOT(ISNUMBER(J17)),J17&lt;B17,J17&gt;TODAY(),K17=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -930,7 +930,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="str">
-        <f aca="false">IF(COUNTA(B18:K18)=0,"",IF(OR(NOT(ISNUMBER(B18)),C18="",D18="",E18="",F18="",G18&lt;1,H18="",I18=""),"ЗАПОЛНИТЬ",IF(I18="Принято","ЗАКРЫТО",IF(I18="Возврат",IF(OR(NOT(ISNUMBER(J18)),J18&lt;B18,K18=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I18="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B18:K18)=0,"",IF(OR(NOT(ISNUMBER(B18)),B18&lt;DATE(2000,1,1),B18&gt;TODAY(),C18="",D18="",E18="",F18="",NOT(AND(ISNUMBER(G18),G18=INT(G18),G18&gt;=1,G18&lt;=10000)),NOT(OR(H18="Подпись на экземпляре",H18="ЭДО",H18="Письмо / курьер",H18="Иное подтверждение")),NOT(OR(I18="На проверке",I18="Принято",I18="Возврат"))),"ЗАПОЛНИТЬ",IF(I18="Принято","ЗАКРЫТО",IF(I18="Возврат",IF(OR(NOT(ISNUMBER(J18)),J18&lt;B18,J18&gt;TODAY(),K18=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -949,7 +949,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5" t="str">
-        <f aca="false">IF(COUNTA(B19:K19)=0,"",IF(OR(NOT(ISNUMBER(B19)),C19="",D19="",E19="",F19="",G19&lt;1,H19="",I19=""),"ЗАПОЛНИТЬ",IF(I19="Принято","ЗАКРЫТО",IF(I19="Возврат",IF(OR(NOT(ISNUMBER(J19)),J19&lt;B19,K19=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I19="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B19:K19)=0,"",IF(OR(NOT(ISNUMBER(B19)),B19&lt;DATE(2000,1,1),B19&gt;TODAY(),C19="",D19="",E19="",F19="",NOT(AND(ISNUMBER(G19),G19=INT(G19),G19&gt;=1,G19&lt;=10000)),NOT(OR(H19="Подпись на экземпляре",H19="ЭДО",H19="Письмо / курьер",H19="Иное подтверждение")),NOT(OR(I19="На проверке",I19="Принято",I19="Возврат"))),"ЗАПОЛНИТЬ",IF(I19="Принято","ЗАКРЫТО",IF(I19="Возврат",IF(OR(NOT(ISNUMBER(J19)),J19&lt;B19,J19&gt;TODAY(),K19=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -968,7 +968,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5" t="str">
-        <f aca="false">IF(COUNTA(B20:K20)=0,"",IF(OR(NOT(ISNUMBER(B20)),C20="",D20="",E20="",F20="",G20&lt;1,H20="",I20=""),"ЗАПОЛНИТЬ",IF(I20="Принято","ЗАКРЫТО",IF(I20="Возврат",IF(OR(NOT(ISNUMBER(J20)),J20&lt;B20,K20=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I20="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B20:K20)=0,"",IF(OR(NOT(ISNUMBER(B20)),B20&lt;DATE(2000,1,1),B20&gt;TODAY(),C20="",D20="",E20="",F20="",NOT(AND(ISNUMBER(G20),G20=INT(G20),G20&gt;=1,G20&lt;=10000)),NOT(OR(H20="Подпись на экземпляре",H20="ЭДО",H20="Письмо / курьер",H20="Иное подтверждение")),NOT(OR(I20="На проверке",I20="Принято",I20="Возврат"))),"ЗАПОЛНИТЬ",IF(I20="Принято","ЗАКРЫТО",IF(I20="Возврат",IF(OR(NOT(ISNUMBER(J20)),J20&lt;B20,J20&gt;TODAY(),K20=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -987,7 +987,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5" t="str">
-        <f aca="false">IF(COUNTA(B21:K21)=0,"",IF(OR(NOT(ISNUMBER(B21)),C21="",D21="",E21="",F21="",G21&lt;1,H21="",I21=""),"ЗАПОЛНИТЬ",IF(I21="Принято","ЗАКРЫТО",IF(I21="Возврат",IF(OR(NOT(ISNUMBER(J21)),J21&lt;B21,K21=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I21="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B21:K21)=0,"",IF(OR(NOT(ISNUMBER(B21)),B21&lt;DATE(2000,1,1),B21&gt;TODAY(),C21="",D21="",E21="",F21="",NOT(AND(ISNUMBER(G21),G21=INT(G21),G21&gt;=1,G21&lt;=10000)),NOT(OR(H21="Подпись на экземпляре",H21="ЭДО",H21="Письмо / курьер",H21="Иное подтверждение")),NOT(OR(I21="На проверке",I21="Принято",I21="Возврат"))),"ЗАПОЛНИТЬ",IF(I21="Принято","ЗАКРЫТО",IF(I21="Возврат",IF(OR(NOT(ISNUMBER(J21)),J21&lt;B21,J21&gt;TODAY(),K21=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5" t="str">
-        <f aca="false">IF(COUNTA(B22:K22)=0,"",IF(OR(NOT(ISNUMBER(B22)),C22="",D22="",E22="",F22="",G22&lt;1,H22="",I22=""),"ЗАПОЛНИТЬ",IF(I22="Принято","ЗАКРЫТО",IF(I22="Возврат",IF(OR(NOT(ISNUMBER(J22)),J22&lt;B22,K22=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I22="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B22:K22)=0,"",IF(OR(NOT(ISNUMBER(B22)),B22&lt;DATE(2000,1,1),B22&gt;TODAY(),C22="",D22="",E22="",F22="",NOT(AND(ISNUMBER(G22),G22=INT(G22),G22&gt;=1,G22&lt;=10000)),NOT(OR(H22="Подпись на экземпляре",H22="ЭДО",H22="Письмо / курьер",H22="Иное подтверждение")),NOT(OR(I22="На проверке",I22="Принято",I22="Возврат"))),"ЗАПОЛНИТЬ",IF(I22="Принято","ЗАКРЫТО",IF(I22="Возврат",IF(OR(NOT(ISNUMBER(J22)),J22&lt;B22,J22&gt;TODAY(),K22=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5" t="str">
-        <f aca="false">IF(COUNTA(B23:K23)=0,"",IF(OR(NOT(ISNUMBER(B23)),C23="",D23="",E23="",F23="",G23&lt;1,H23="",I23=""),"ЗАПОЛНИТЬ",IF(I23="Принято","ЗАКРЫТО",IF(I23="Возврат",IF(OR(NOT(ISNUMBER(J23)),J23&lt;B23,K23=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I23="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B23:K23)=0,"",IF(OR(NOT(ISNUMBER(B23)),B23&lt;DATE(2000,1,1),B23&gt;TODAY(),C23="",D23="",E23="",F23="",NOT(AND(ISNUMBER(G23),G23=INT(G23),G23&gt;=1,G23&lt;=10000)),NOT(OR(H23="Подпись на экземпляре",H23="ЭДО",H23="Письмо / курьер",H23="Иное подтверждение")),NOT(OR(I23="На проверке",I23="Принято",I23="Возврат"))),"ЗАПОЛНИТЬ",IF(I23="Принято","ЗАКРЫТО",IF(I23="Возврат",IF(OR(NOT(ISNUMBER(J23)),J23&lt;B23,J23&gt;TODAY(),K23=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5" t="str">
-        <f aca="false">IF(COUNTA(B24:K24)=0,"",IF(OR(NOT(ISNUMBER(B24)),C24="",D24="",E24="",F24="",G24&lt;1,H24="",I24=""),"ЗАПОЛНИТЬ",IF(I24="Принято","ЗАКРЫТО",IF(I24="Возврат",IF(OR(NOT(ISNUMBER(J24)),J24&lt;B24,K24=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I24="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B24:K24)=0,"",IF(OR(NOT(ISNUMBER(B24)),B24&lt;DATE(2000,1,1),B24&gt;TODAY(),C24="",D24="",E24="",F24="",NOT(AND(ISNUMBER(G24),G24=INT(G24),G24&gt;=1,G24&lt;=10000)),NOT(OR(H24="Подпись на экземпляре",H24="ЭДО",H24="Письмо / курьер",H24="Иное подтверждение")),NOT(OR(I24="На проверке",I24="Принято",I24="Возврат"))),"ЗАПОЛНИТЬ",IF(I24="Принято","ЗАКРЫТО",IF(I24="Возврат",IF(OR(NOT(ISNUMBER(J24)),J24&lt;B24,J24&gt;TODAY(),K24=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="str">
-        <f aca="false">IF(COUNTA(B25:K25)=0,"",IF(OR(NOT(ISNUMBER(B25)),C25="",D25="",E25="",F25="",G25&lt;1,H25="",I25=""),"ЗАПОЛНИТЬ",IF(I25="Принято","ЗАКРЫТО",IF(I25="Возврат",IF(OR(NOT(ISNUMBER(J25)),J25&lt;B25,K25=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I25="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B25:K25)=0,"",IF(OR(NOT(ISNUMBER(B25)),B25&lt;DATE(2000,1,1),B25&gt;TODAY(),C25="",D25="",E25="",F25="",NOT(AND(ISNUMBER(G25),G25=INT(G25),G25&gt;=1,G25&lt;=10000)),NOT(OR(H25="Подпись на экземпляре",H25="ЭДО",H25="Письмо / курьер",H25="Иное подтверждение")),NOT(OR(I25="На проверке",I25="Принято",I25="Возврат"))),"ЗАПОЛНИТЬ",IF(I25="Принято","ЗАКРЫТО",IF(I25="Возврат",IF(OR(NOT(ISNUMBER(J25)),J25&lt;B25,J25&gt;TODAY(),K25=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="str">
-        <f aca="false">IF(COUNTA(B26:K26)=0,"",IF(OR(NOT(ISNUMBER(B26)),C26="",D26="",E26="",F26="",G26&lt;1,H26="",I26=""),"ЗАПОЛНИТЬ",IF(I26="Принято","ЗАКРЫТО",IF(I26="Возврат",IF(OR(NOT(ISNUMBER(J26)),J26&lt;B26,K26=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I26="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B26:K26)=0,"",IF(OR(NOT(ISNUMBER(B26)),B26&lt;DATE(2000,1,1),B26&gt;TODAY(),C26="",D26="",E26="",F26="",NOT(AND(ISNUMBER(G26),G26=INT(G26),G26&gt;=1,G26&lt;=10000)),NOT(OR(H26="Подпись на экземпляре",H26="ЭДО",H26="Письмо / курьер",H26="Иное подтверждение")),NOT(OR(I26="На проверке",I26="Принято",I26="Возврат"))),"ЗАПОЛНИТЬ",IF(I26="Принято","ЗАКРЫТО",IF(I26="Возврат",IF(OR(NOT(ISNUMBER(J26)),J26&lt;B26,J26&gt;TODAY(),K26=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="str">
-        <f aca="false">IF(COUNTA(B27:K27)=0,"",IF(OR(NOT(ISNUMBER(B27)),C27="",D27="",E27="",F27="",G27&lt;1,H27="",I27=""),"ЗАПОЛНИТЬ",IF(I27="Принято","ЗАКРЫТО",IF(I27="Возврат",IF(OR(NOT(ISNUMBER(J27)),J27&lt;B27,K27=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I27="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B27:K27)=0,"",IF(OR(NOT(ISNUMBER(B27)),B27&lt;DATE(2000,1,1),B27&gt;TODAY(),C27="",D27="",E27="",F27="",NOT(AND(ISNUMBER(G27),G27=INT(G27),G27&gt;=1,G27&lt;=10000)),NOT(OR(H27="Подпись на экземпляре",H27="ЭДО",H27="Письмо / курьер",H27="Иное подтверждение")),NOT(OR(I27="На проверке",I27="Принято",I27="Возврат"))),"ЗАПОЛНИТЬ",IF(I27="Принято","ЗАКРЫТО",IF(I27="Возврат",IF(OR(NOT(ISNUMBER(J27)),J27&lt;B27,J27&gt;TODAY(),K27=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="str">
-        <f aca="false">IF(COUNTA(B28:K28)=0,"",IF(OR(NOT(ISNUMBER(B28)),C28="",D28="",E28="",F28="",G28&lt;1,H28="",I28=""),"ЗАПОЛНИТЬ",IF(I28="Принято","ЗАКРЫТО",IF(I28="Возврат",IF(OR(NOT(ISNUMBER(J28)),J28&lt;B28,K28=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I28="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B28:K28)=0,"",IF(OR(NOT(ISNUMBER(B28)),B28&lt;DATE(2000,1,1),B28&gt;TODAY(),C28="",D28="",E28="",F28="",NOT(AND(ISNUMBER(G28),G28=INT(G28),G28&gt;=1,G28&lt;=10000)),NOT(OR(H28="Подпись на экземпляре",H28="ЭДО",H28="Письмо / курьер",H28="Иное подтверждение")),NOT(OR(I28="На проверке",I28="Принято",I28="Возврат"))),"ЗАПОЛНИТЬ",IF(I28="Принято","ЗАКРЫТО",IF(I28="Возврат",IF(OR(NOT(ISNUMBER(J28)),J28&lt;B28,J28&gt;TODAY(),K28=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5" t="str">
-        <f aca="false">IF(COUNTA(B29:K29)=0,"",IF(OR(NOT(ISNUMBER(B29)),C29="",D29="",E29="",F29="",G29&lt;1,H29="",I29=""),"ЗАПОЛНИТЬ",IF(I29="Принято","ЗАКРЫТО",IF(I29="Возврат",IF(OR(NOT(ISNUMBER(J29)),J29&lt;B29,K29=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I29="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B29:K29)=0,"",IF(OR(NOT(ISNUMBER(B29)),B29&lt;DATE(2000,1,1),B29&gt;TODAY(),C29="",D29="",E29="",F29="",NOT(AND(ISNUMBER(G29),G29=INT(G29),G29&gt;=1,G29&lt;=10000)),NOT(OR(H29="Подпись на экземпляре",H29="ЭДО",H29="Письмо / курьер",H29="Иное подтверждение")),NOT(OR(I29="На проверке",I29="Принято",I29="Возврат"))),"ЗАПОЛНИТЬ",IF(I29="Принято","ЗАКРЫТО",IF(I29="Возврат",IF(OR(NOT(ISNUMBER(J29)),J29&lt;B29,J29&gt;TODAY(),K29=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="str">
-        <f aca="false">IF(COUNTA(B30:K30)=0,"",IF(OR(NOT(ISNUMBER(B30)),C30="",D30="",E30="",F30="",G30&lt;1,H30="",I30=""),"ЗАПОЛНИТЬ",IF(I30="Принято","ЗАКРЫТО",IF(I30="Возврат",IF(OR(NOT(ISNUMBER(J30)),J30&lt;B30,K30=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I30="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B30:K30)=0,"",IF(OR(NOT(ISNUMBER(B30)),B30&lt;DATE(2000,1,1),B30&gt;TODAY(),C30="",D30="",E30="",F30="",NOT(AND(ISNUMBER(G30),G30=INT(G30),G30&gt;=1,G30&lt;=10000)),NOT(OR(H30="Подпись на экземпляре",H30="ЭДО",H30="Письмо / курьер",H30="Иное подтверждение")),NOT(OR(I30="На проверке",I30="Принято",I30="Возврат"))),"ЗАПОЛНИТЬ",IF(I30="Принято","ЗАКРЫТО",IF(I30="Возврат",IF(OR(NOT(ISNUMBER(J30)),J30&lt;B30,J30&gt;TODAY(),K30=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="str">
-        <f aca="false">IF(COUNTA(B31:K31)=0,"",IF(OR(NOT(ISNUMBER(B31)),C31="",D31="",E31="",F31="",G31&lt;1,H31="",I31=""),"ЗАПОЛНИТЬ",IF(I31="Принято","ЗАКРЫТО",IF(I31="Возврат",IF(OR(NOT(ISNUMBER(J31)),J31&lt;B31,K31=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I31="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B31:K31)=0,"",IF(OR(NOT(ISNUMBER(B31)),B31&lt;DATE(2000,1,1),B31&gt;TODAY(),C31="",D31="",E31="",F31="",NOT(AND(ISNUMBER(G31),G31=INT(G31),G31&gt;=1,G31&lt;=10000)),NOT(OR(H31="Подпись на экземпляре",H31="ЭДО",H31="Письмо / курьер",H31="Иное подтверждение")),NOT(OR(I31="На проверке",I31="Принято",I31="Возврат"))),"ЗАПОЛНИТЬ",IF(I31="Принято","ЗАКРЫТО",IF(I31="Возврат",IF(OR(NOT(ISNUMBER(J31)),J31&lt;B31,J31&gt;TODAY(),K31=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="str">
-        <f aca="false">IF(COUNTA(B32:K32)=0,"",IF(OR(NOT(ISNUMBER(B32)),C32="",D32="",E32="",F32="",G32&lt;1,H32="",I32=""),"ЗАПОЛНИТЬ",IF(I32="Принято","ЗАКРЫТО",IF(I32="Возврат",IF(OR(NOT(ISNUMBER(J32)),J32&lt;B32,K32=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I32="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B32:K32)=0,"",IF(OR(NOT(ISNUMBER(B32)),B32&lt;DATE(2000,1,1),B32&gt;TODAY(),C32="",D32="",E32="",F32="",NOT(AND(ISNUMBER(G32),G32=INT(G32),G32&gt;=1,G32&lt;=10000)),NOT(OR(H32="Подпись на экземпляре",H32="ЭДО",H32="Письмо / курьер",H32="Иное подтверждение")),NOT(OR(I32="На проверке",I32="Принято",I32="Возврат"))),"ЗАПОЛНИТЬ",IF(I32="Принято","ЗАКРЫТО",IF(I32="Возврат",IF(OR(NOT(ISNUMBER(J32)),J32&lt;B32,J32&gt;TODAY(),K32=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="str">
-        <f aca="false">IF(COUNTA(B33:K33)=0,"",IF(OR(NOT(ISNUMBER(B33)),C33="",D33="",E33="",F33="",G33&lt;1,H33="",I33=""),"ЗАПОЛНИТЬ",IF(I33="Принято","ЗАКРЫТО",IF(I33="Возврат",IF(OR(NOT(ISNUMBER(J33)),J33&lt;B33,K33=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I33="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B33:K33)=0,"",IF(OR(NOT(ISNUMBER(B33)),B33&lt;DATE(2000,1,1),B33&gt;TODAY(),C33="",D33="",E33="",F33="",NOT(AND(ISNUMBER(G33),G33=INT(G33),G33&gt;=1,G33&lt;=10000)),NOT(OR(H33="Подпись на экземпляре",H33="ЭДО",H33="Письмо / курьер",H33="Иное подтверждение")),NOT(OR(I33="На проверке",I33="Принято",I33="Возврат"))),"ЗАПОЛНИТЬ",IF(I33="Принято","ЗАКРЫТО",IF(I33="Возврат",IF(OR(NOT(ISNUMBER(J33)),J33&lt;B33,J33&gt;TODAY(),K33=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="str">
-        <f aca="false">IF(COUNTA(B34:K34)=0,"",IF(OR(NOT(ISNUMBER(B34)),C34="",D34="",E34="",F34="",G34&lt;1,H34="",I34=""),"ЗАПОЛНИТЬ",IF(I34="Принято","ЗАКРЫТО",IF(I34="Возврат",IF(OR(NOT(ISNUMBER(J34)),J34&lt;B34,K34=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I34="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B34:K34)=0,"",IF(OR(NOT(ISNUMBER(B34)),B34&lt;DATE(2000,1,1),B34&gt;TODAY(),C34="",D34="",E34="",F34="",NOT(AND(ISNUMBER(G34),G34=INT(G34),G34&gt;=1,G34&lt;=10000)),NOT(OR(H34="Подпись на экземпляре",H34="ЭДО",H34="Письмо / курьер",H34="Иное подтверждение")),NOT(OR(I34="На проверке",I34="Принято",I34="Возврат"))),"ЗАПОЛНИТЬ",IF(I34="Принято","ЗАКРЫТО",IF(I34="Возврат",IF(OR(NOT(ISNUMBER(J34)),J34&lt;B34,J34&gt;TODAY(),K34=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="str">
-        <f aca="false">IF(COUNTA(B35:K35)=0,"",IF(OR(NOT(ISNUMBER(B35)),C35="",D35="",E35="",F35="",G35&lt;1,H35="",I35=""),"ЗАПОЛНИТЬ",IF(I35="Принято","ЗАКРЫТО",IF(I35="Возврат",IF(OR(NOT(ISNUMBER(J35)),J35&lt;B35,K35=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I35="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B35:K35)=0,"",IF(OR(NOT(ISNUMBER(B35)),B35&lt;DATE(2000,1,1),B35&gt;TODAY(),C35="",D35="",E35="",F35="",NOT(AND(ISNUMBER(G35),G35=INT(G35),G35&gt;=1,G35&lt;=10000)),NOT(OR(H35="Подпись на экземпляре",H35="ЭДО",H35="Письмо / курьер",H35="Иное подтверждение")),NOT(OR(I35="На проверке",I35="Принято",I35="Возврат"))),"ЗАПОЛНИТЬ",IF(I35="Принято","ЗАКРЫТО",IF(I35="Возврат",IF(OR(NOT(ISNUMBER(J35)),J35&lt;B35,J35&gt;TODAY(),K35=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="str">
-        <f aca="false">IF(COUNTA(B36:K36)=0,"",IF(OR(NOT(ISNUMBER(B36)),C36="",D36="",E36="",F36="",G36&lt;1,H36="",I36=""),"ЗАПОЛНИТЬ",IF(I36="Принято","ЗАКРЫТО",IF(I36="Возврат",IF(OR(NOT(ISNUMBER(J36)),J36&lt;B36,K36=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I36="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B36:K36)=0,"",IF(OR(NOT(ISNUMBER(B36)),B36&lt;DATE(2000,1,1),B36&gt;TODAY(),C36="",D36="",E36="",F36="",NOT(AND(ISNUMBER(G36),G36=INT(G36),G36&gt;=1,G36&lt;=10000)),NOT(OR(H36="Подпись на экземпляре",H36="ЭДО",H36="Письмо / курьер",H36="Иное подтверждение")),NOT(OR(I36="На проверке",I36="Принято",I36="Возврат"))),"ЗАПОЛНИТЬ",IF(I36="Принято","ЗАКРЫТО",IF(I36="Возврат",IF(OR(NOT(ISNUMBER(J36)),J36&lt;B36,J36&gt;TODAY(),K36=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="str">
-        <f aca="false">IF(COUNTA(B37:K37)=0,"",IF(OR(NOT(ISNUMBER(B37)),C37="",D37="",E37="",F37="",G37&lt;1,H37="",I37=""),"ЗАПОЛНИТЬ",IF(I37="Принято","ЗАКРЫТО",IF(I37="Возврат",IF(OR(NOT(ISNUMBER(J37)),J37&lt;B37,K37=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I37="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B37:K37)=0,"",IF(OR(NOT(ISNUMBER(B37)),B37&lt;DATE(2000,1,1),B37&gt;TODAY(),C37="",D37="",E37="",F37="",NOT(AND(ISNUMBER(G37),G37=INT(G37),G37&gt;=1,G37&lt;=10000)),NOT(OR(H37="Подпись на экземпляре",H37="ЭДО",H37="Письмо / курьер",H37="Иное подтверждение")),NOT(OR(I37="На проверке",I37="Принято",I37="Возврат"))),"ЗАПОЛНИТЬ",IF(I37="Принято","ЗАКРЫТО",IF(I37="Возврат",IF(OR(NOT(ISNUMBER(J37)),J37&lt;B37,J37&gt;TODAY(),K37=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="str">
-        <f aca="false">IF(COUNTA(B38:K38)=0,"",IF(OR(NOT(ISNUMBER(B38)),C38="",D38="",E38="",F38="",G38&lt;1,H38="",I38=""),"ЗАПОЛНИТЬ",IF(I38="Принято","ЗАКРЫТО",IF(I38="Возврат",IF(OR(NOT(ISNUMBER(J38)),J38&lt;B38,K38=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I38="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B38:K38)=0,"",IF(OR(NOT(ISNUMBER(B38)),B38&lt;DATE(2000,1,1),B38&gt;TODAY(),C38="",D38="",E38="",F38="",NOT(AND(ISNUMBER(G38),G38=INT(G38),G38&gt;=1,G38&lt;=10000)),NOT(OR(H38="Подпись на экземпляре",H38="ЭДО",H38="Письмо / курьер",H38="Иное подтверждение")),NOT(OR(I38="На проверке",I38="Принято",I38="Возврат"))),"ЗАПОЛНИТЬ",IF(I38="Принято","ЗАКРЫТО",IF(I38="Возврат",IF(OR(NOT(ISNUMBER(J38)),J38&lt;B38,J38&gt;TODAY(),K38=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="str">
-        <f aca="false">IF(COUNTA(B39:K39)=0,"",IF(OR(NOT(ISNUMBER(B39)),C39="",D39="",E39="",F39="",G39&lt;1,H39="",I39=""),"ЗАПОЛНИТЬ",IF(I39="Принято","ЗАКРЫТО",IF(I39="Возврат",IF(OR(NOT(ISNUMBER(J39)),J39&lt;B39,K39=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I39="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B39:K39)=0,"",IF(OR(NOT(ISNUMBER(B39)),B39&lt;DATE(2000,1,1),B39&gt;TODAY(),C39="",D39="",E39="",F39="",NOT(AND(ISNUMBER(G39),G39=INT(G39),G39&gt;=1,G39&lt;=10000)),NOT(OR(H39="Подпись на экземпляре",H39="ЭДО",H39="Письмо / курьер",H39="Иное подтверждение")),NOT(OR(I39="На проверке",I39="Принято",I39="Возврат"))),"ЗАПОЛНИТЬ",IF(I39="Принято","ЗАКРЫТО",IF(I39="Возврат",IF(OR(NOT(ISNUMBER(J39)),J39&lt;B39,J39&gt;TODAY(),K39=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5" t="str">
-        <f aca="false">IF(COUNTA(B40:K40)=0,"",IF(OR(NOT(ISNUMBER(B40)),C40="",D40="",E40="",F40="",G40&lt;1,H40="",I40=""),"ЗАПОЛНИТЬ",IF(I40="Принято","ЗАКРЫТО",IF(I40="Возврат",IF(OR(NOT(ISNUMBER(J40)),J40&lt;B40,K40=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I40="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B40:K40)=0,"",IF(OR(NOT(ISNUMBER(B40)),B40&lt;DATE(2000,1,1),B40&gt;TODAY(),C40="",D40="",E40="",F40="",NOT(AND(ISNUMBER(G40),G40=INT(G40),G40&gt;=1,G40&lt;=10000)),NOT(OR(H40="Подпись на экземпляре",H40="ЭДО",H40="Письмо / курьер",H40="Иное подтверждение")),NOT(OR(I40="На проверке",I40="Принято",I40="Возврат"))),"ЗАПОЛНИТЬ",IF(I40="Принято","ЗАКРЫТО",IF(I40="Возврат",IF(OR(NOT(ISNUMBER(J40)),J40&lt;B40,J40&gt;TODAY(),K40=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="str">
-        <f aca="false">IF(COUNTA(B41:K41)=0,"",IF(OR(NOT(ISNUMBER(B41)),C41="",D41="",E41="",F41="",G41&lt;1,H41="",I41=""),"ЗАПОЛНИТЬ",IF(I41="Принято","ЗАКРЫТО",IF(I41="Возврат",IF(OR(NOT(ISNUMBER(J41)),J41&lt;B41,K41=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I41="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B41:K41)=0,"",IF(OR(NOT(ISNUMBER(B41)),B41&lt;DATE(2000,1,1),B41&gt;TODAY(),C41="",D41="",E41="",F41="",NOT(AND(ISNUMBER(G41),G41=INT(G41),G41&gt;=1,G41&lt;=10000)),NOT(OR(H41="Подпись на экземпляре",H41="ЭДО",H41="Письмо / курьер",H41="Иное подтверждение")),NOT(OR(I41="На проверке",I41="Принято",I41="Возврат"))),"ЗАПОЛНИТЬ",IF(I41="Принято","ЗАКРЫТО",IF(I41="Возврат",IF(OR(NOT(ISNUMBER(J41)),J41&lt;B41,J41&gt;TODAY(),K41=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5" t="str">
-        <f aca="false">IF(COUNTA(B42:K42)=0,"",IF(OR(NOT(ISNUMBER(B42)),C42="",D42="",E42="",F42="",G42&lt;1,H42="",I42=""),"ЗАПОЛНИТЬ",IF(I42="Принято","ЗАКРЫТО",IF(I42="Возврат",IF(OR(NOT(ISNUMBER(J42)),J42&lt;B42,K42=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I42="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B42:K42)=0,"",IF(OR(NOT(ISNUMBER(B42)),B42&lt;DATE(2000,1,1),B42&gt;TODAY(),C42="",D42="",E42="",F42="",NOT(AND(ISNUMBER(G42),G42=INT(G42),G42&gt;=1,G42&lt;=10000)),NOT(OR(H42="Подпись на экземпляре",H42="ЭДО",H42="Письмо / курьер",H42="Иное подтверждение")),NOT(OR(I42="На проверке",I42="Принято",I42="Возврат"))),"ЗАПОЛНИТЬ",IF(I42="Принято","ЗАКРЫТО",IF(I42="Возврат",IF(OR(NOT(ISNUMBER(J42)),J42&lt;B42,J42&gt;TODAY(),K42=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5" t="str">
-        <f aca="false">IF(COUNTA(B43:K43)=0,"",IF(OR(NOT(ISNUMBER(B43)),C43="",D43="",E43="",F43="",G43&lt;1,H43="",I43=""),"ЗАПОЛНИТЬ",IF(I43="Принято","ЗАКРЫТО",IF(I43="Возврат",IF(OR(NOT(ISNUMBER(J43)),J43&lt;B43,K43=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I43="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B43:K43)=0,"",IF(OR(NOT(ISNUMBER(B43)),B43&lt;DATE(2000,1,1),B43&gt;TODAY(),C43="",D43="",E43="",F43="",NOT(AND(ISNUMBER(G43),G43=INT(G43),G43&gt;=1,G43&lt;=10000)),NOT(OR(H43="Подпись на экземпляре",H43="ЭДО",H43="Письмо / курьер",H43="Иное подтверждение")),NOT(OR(I43="На проверке",I43="Принято",I43="Возврат"))),"ЗАПОЛНИТЬ",IF(I43="Принято","ЗАКРЫТО",IF(I43="Возврат",IF(OR(NOT(ISNUMBER(J43)),J43&lt;B43,J43&gt;TODAY(),K43=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5" t="str">
-        <f aca="false">IF(COUNTA(B44:K44)=0,"",IF(OR(NOT(ISNUMBER(B44)),C44="",D44="",E44="",F44="",G44&lt;1,H44="",I44=""),"ЗАПОЛНИТЬ",IF(I44="Принято","ЗАКРЫТО",IF(I44="Возврат",IF(OR(NOT(ISNUMBER(J44)),J44&lt;B44,K44=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I44="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B44:K44)=0,"",IF(OR(NOT(ISNUMBER(B44)),B44&lt;DATE(2000,1,1),B44&gt;TODAY(),C44="",D44="",E44="",F44="",NOT(AND(ISNUMBER(G44),G44=INT(G44),G44&gt;=1,G44&lt;=10000)),NOT(OR(H44="Подпись на экземпляре",H44="ЭДО",H44="Письмо / курьер",H44="Иное подтверждение")),NOT(OR(I44="На проверке",I44="Принято",I44="Возврат"))),"ЗАПОЛНИТЬ",IF(I44="Принято","ЗАКРЫТО",IF(I44="Возврат",IF(OR(NOT(ISNUMBER(J44)),J44&lt;B44,J44&gt;TODAY(),K44=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5" t="str">
-        <f aca="false">IF(COUNTA(B45:K45)=0,"",IF(OR(NOT(ISNUMBER(B45)),C45="",D45="",E45="",F45="",G45&lt;1,H45="",I45=""),"ЗАПОЛНИТЬ",IF(I45="Принято","ЗАКРЫТО",IF(I45="Возврат",IF(OR(NOT(ISNUMBER(J45)),J45&lt;B45,K45=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I45="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B45:K45)=0,"",IF(OR(NOT(ISNUMBER(B45)),B45&lt;DATE(2000,1,1),B45&gt;TODAY(),C45="",D45="",E45="",F45="",NOT(AND(ISNUMBER(G45),G45=INT(G45),G45&gt;=1,G45&lt;=10000)),NOT(OR(H45="Подпись на экземпляре",H45="ЭДО",H45="Письмо / курьер",H45="Иное подтверждение")),NOT(OR(I45="На проверке",I45="Принято",I45="Возврат"))),"ЗАПОЛНИТЬ",IF(I45="Принято","ЗАКРЫТО",IF(I45="Возврат",IF(OR(NOT(ISNUMBER(J45)),J45&lt;B45,J45&gt;TODAY(),K45=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5" t="str">
-        <f aca="false">IF(COUNTA(B46:K46)=0,"",IF(OR(NOT(ISNUMBER(B46)),C46="",D46="",E46="",F46="",G46&lt;1,H46="",I46=""),"ЗАПОЛНИТЬ",IF(I46="Принято","ЗАКРЫТО",IF(I46="Возврат",IF(OR(NOT(ISNUMBER(J46)),J46&lt;B46,K46=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I46="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B46:K46)=0,"",IF(OR(NOT(ISNUMBER(B46)),B46&lt;DATE(2000,1,1),B46&gt;TODAY(),C46="",D46="",E46="",F46="",NOT(AND(ISNUMBER(G46),G46=INT(G46),G46&gt;=1,G46&lt;=10000)),NOT(OR(H46="Подпись на экземпляре",H46="ЭДО",H46="Письмо / курьер",H46="Иное подтверждение")),NOT(OR(I46="На проверке",I46="Принято",I46="Возврат"))),"ЗАПОЛНИТЬ",IF(I46="Принято","ЗАКРЫТО",IF(I46="Возврат",IF(OR(NOT(ISNUMBER(J46)),J46&lt;B46,J46&gt;TODAY(),K46=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5" t="str">
-        <f aca="false">IF(COUNTA(B47:K47)=0,"",IF(OR(NOT(ISNUMBER(B47)),C47="",D47="",E47="",F47="",G47&lt;1,H47="",I47=""),"ЗАПОЛНИТЬ",IF(I47="Принято","ЗАКРЫТО",IF(I47="Возврат",IF(OR(NOT(ISNUMBER(J47)),J47&lt;B47,K47=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I47="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B47:K47)=0,"",IF(OR(NOT(ISNUMBER(B47)),B47&lt;DATE(2000,1,1),B47&gt;TODAY(),C47="",D47="",E47="",F47="",NOT(AND(ISNUMBER(G47),G47=INT(G47),G47&gt;=1,G47&lt;=10000)),NOT(OR(H47="Подпись на экземпляре",H47="ЭДО",H47="Письмо / курьер",H47="Иное подтверждение")),NOT(OR(I47="На проверке",I47="Принято",I47="Возврат"))),"ЗАПОЛНИТЬ",IF(I47="Принято","ЗАКРЫТО",IF(I47="Возврат",IF(OR(NOT(ISNUMBER(J47)),J47&lt;B47,J47&gt;TODAY(),K47=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5" t="str">
-        <f aca="false">IF(COUNTA(B48:K48)=0,"",IF(OR(NOT(ISNUMBER(B48)),C48="",D48="",E48="",F48="",G48&lt;1,H48="",I48=""),"ЗАПОЛНИТЬ",IF(I48="Принято","ЗАКРЫТО",IF(I48="Возврат",IF(OR(NOT(ISNUMBER(J48)),J48&lt;B48,K48=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I48="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B48:K48)=0,"",IF(OR(NOT(ISNUMBER(B48)),B48&lt;DATE(2000,1,1),B48&gt;TODAY(),C48="",D48="",E48="",F48="",NOT(AND(ISNUMBER(G48),G48=INT(G48),G48&gt;=1,G48&lt;=10000)),NOT(OR(H48="Подпись на экземпляре",H48="ЭДО",H48="Письмо / курьер",H48="Иное подтверждение")),NOT(OR(I48="На проверке",I48="Принято",I48="Возврат"))),"ЗАПОЛНИТЬ",IF(I48="Принято","ЗАКРЫТО",IF(I48="Возврат",IF(OR(NOT(ISNUMBER(J48)),J48&lt;B48,J48&gt;TODAY(),K48=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5" t="str">
-        <f aca="false">IF(COUNTA(B49:K49)=0,"",IF(OR(NOT(ISNUMBER(B49)),C49="",D49="",E49="",F49="",G49&lt;1,H49="",I49=""),"ЗАПОЛНИТЬ",IF(I49="Принято","ЗАКРЫТО",IF(I49="Возврат",IF(OR(NOT(ISNUMBER(J49)),J49&lt;B49,K49=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I49="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B49:K49)=0,"",IF(OR(NOT(ISNUMBER(B49)),B49&lt;DATE(2000,1,1),B49&gt;TODAY(),C49="",D49="",E49="",F49="",NOT(AND(ISNUMBER(G49),G49=INT(G49),G49&gt;=1,G49&lt;=10000)),NOT(OR(H49="Подпись на экземпляре",H49="ЭДО",H49="Письмо / курьер",H49="Иное подтверждение")),NOT(OR(I49="На проверке",I49="Принято",I49="Возврат"))),"ЗАПОЛНИТЬ",IF(I49="Принято","ЗАКРЫТО",IF(I49="Возврат",IF(OR(NOT(ISNUMBER(J49)),J49&lt;B49,J49&gt;TODAY(),K49=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5" t="str">
-        <f aca="false">IF(COUNTA(B50:K50)=0,"",IF(OR(NOT(ISNUMBER(B50)),C50="",D50="",E50="",F50="",G50&lt;1,H50="",I50=""),"ЗАПОЛНИТЬ",IF(I50="Принято","ЗАКРЫТО",IF(I50="Возврат",IF(OR(NOT(ISNUMBER(J50)),J50&lt;B50,K50=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I50="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B50:K50)=0,"",IF(OR(NOT(ISNUMBER(B50)),B50&lt;DATE(2000,1,1),B50&gt;TODAY(),C50="",D50="",E50="",F50="",NOT(AND(ISNUMBER(G50),G50=INT(G50),G50&gt;=1,G50&lt;=10000)),NOT(OR(H50="Подпись на экземпляре",H50="ЭДО",H50="Письмо / курьер",H50="Иное подтверждение")),NOT(OR(I50="На проверке",I50="Принято",I50="Возврат"))),"ЗАПОЛНИТЬ",IF(I50="Принято","ЗАКРЫТО",IF(I50="Возврат",IF(OR(NOT(ISNUMBER(J50)),J50&lt;B50,J50&gt;TODAY(),K50=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5" t="str">
-        <f aca="false">IF(COUNTA(B51:K51)=0,"",IF(OR(NOT(ISNUMBER(B51)),C51="",D51="",E51="",F51="",G51&lt;1,H51="",I51=""),"ЗАПОЛНИТЬ",IF(I51="Принято","ЗАКРЫТО",IF(I51="Возврат",IF(OR(NOT(ISNUMBER(J51)),J51&lt;B51,K51=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I51="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B51:K51)=0,"",IF(OR(NOT(ISNUMBER(B51)),B51&lt;DATE(2000,1,1),B51&gt;TODAY(),C51="",D51="",E51="",F51="",NOT(AND(ISNUMBER(G51),G51=INT(G51),G51&gt;=1,G51&lt;=10000)),NOT(OR(H51="Подпись на экземпляре",H51="ЭДО",H51="Письмо / курьер",H51="Иное подтверждение")),NOT(OR(I51="На проверке",I51="Принято",I51="Возврат"))),"ЗАПОЛНИТЬ",IF(I51="Принято","ЗАКРЫТО",IF(I51="Возврат",IF(OR(NOT(ISNUMBER(J51)),J51&lt;B51,J51&gt;TODAY(),K51=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5" t="str">
-        <f aca="false">IF(COUNTA(B52:K52)=0,"",IF(OR(NOT(ISNUMBER(B52)),C52="",D52="",E52="",F52="",G52&lt;1,H52="",I52=""),"ЗАПОЛНИТЬ",IF(I52="Принято","ЗАКРЫТО",IF(I52="Возврат",IF(OR(NOT(ISNUMBER(J52)),J52&lt;B52,K52=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I52="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B52:K52)=0,"",IF(OR(NOT(ISNUMBER(B52)),B52&lt;DATE(2000,1,1),B52&gt;TODAY(),C52="",D52="",E52="",F52="",NOT(AND(ISNUMBER(G52),G52=INT(G52),G52&gt;=1,G52&lt;=10000)),NOT(OR(H52="Подпись на экземпляре",H52="ЭДО",H52="Письмо / курьер",H52="Иное подтверждение")),NOT(OR(I52="На проверке",I52="Принято",I52="Возврат"))),"ЗАПОЛНИТЬ",IF(I52="Принято","ЗАКРЫТО",IF(I52="Возврат",IF(OR(NOT(ISNUMBER(J52)),J52&lt;B52,J52&gt;TODAY(),K52=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5" t="str">
-        <f aca="false">IF(COUNTA(B53:K53)=0,"",IF(OR(NOT(ISNUMBER(B53)),C53="",D53="",E53="",F53="",G53&lt;1,H53="",I53=""),"ЗАПОЛНИТЬ",IF(I53="Принято","ЗАКРЫТО",IF(I53="Возврат",IF(OR(NOT(ISNUMBER(J53)),J53&lt;B53,K53=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I53="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B53:K53)=0,"",IF(OR(NOT(ISNUMBER(B53)),B53&lt;DATE(2000,1,1),B53&gt;TODAY(),C53="",D53="",E53="",F53="",NOT(AND(ISNUMBER(G53),G53=INT(G53),G53&gt;=1,G53&lt;=10000)),NOT(OR(H53="Подпись на экземпляре",H53="ЭДО",H53="Письмо / курьер",H53="Иное подтверждение")),NOT(OR(I53="На проверке",I53="Принято",I53="Возврат"))),"ЗАПОЛНИТЬ",IF(I53="Принято","ЗАКРЫТО",IF(I53="Возврат",IF(OR(NOT(ISNUMBER(J53)),J53&lt;B53,J53&gt;TODAY(),K53=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5" t="str">
-        <f aca="false">IF(COUNTA(B54:K54)=0,"",IF(OR(NOT(ISNUMBER(B54)),C54="",D54="",E54="",F54="",G54&lt;1,H54="",I54=""),"ЗАПОЛНИТЬ",IF(I54="Принято","ЗАКРЫТО",IF(I54="Возврат",IF(OR(NOT(ISNUMBER(J54)),J54&lt;B54,K54=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),IF(I54="На проверке","В РАБОТЕ","ПРОВЕРИТЬ")))))</f>
+        <f aca="true">IF(COUNTA(B54:K54)=0,"",IF(OR(NOT(ISNUMBER(B54)),B54&lt;DATE(2000,1,1),B54&gt;TODAY(),C54="",D54="",E54="",F54="",NOT(AND(ISNUMBER(G54),G54=INT(G54),G54&gt;=1,G54&lt;=10000)),NOT(OR(H54="Подпись на экземпляре",H54="ЭДО",H54="Письмо / курьер",H54="Иное подтверждение")),NOT(OR(I54="На проверке",I54="Принято",I54="Возврат"))),"ЗАПОЛНИТЬ",IF(I54="Принято","ЗАКРЫТО",IF(I54="Возврат",IF(OR(NOT(ISNUMBER(J54)),J54&lt;B54,J54&gt;TODAY(),K54=""),"УКАЗАТЬ ВОЗВРАТ","ВОЗВРАТ ЗАФИКСИРОВАН"),"В РАБОТЕ"))))</f>
         <v/>
       </c>
     </row>
@@ -1625,44 +1625,53 @@
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="L5:L54">
-    <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="ГОТОВО" dxfId="4">
-      <formula>NOT(ISERROR(SEARCH("ГОТОВО",L5)))</formula>
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>$L5="ГОТОВО"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="3" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="ЗАПОЛНИТЬ" dxfId="5">
-      <formula>NOT(ISERROR(SEARCH("ЗАПОЛНИТЬ",L5)))</formula>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>$L5="ЗАКРЫТО"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="4" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="НЕ ГОТОВО" dxfId="5">
-      <formula>NOT(ISERROR(SEARCH("НЕ ГОТОВО",L5)))</formula>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>$L5="НЕ ГОТОВО"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="5" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="ПРОВЕРИТЬ" dxfId="6">
-      <formula>NOT(ISERROR(SEARCH("ПРОВЕРИТЬ",L5)))</formula>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>$L5="ЗАПОЛНИТЬ"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="6" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="ВОЗВРАТ" dxfId="6">
-      <formula>NOT(ISERROR(SEARCH("ВОЗВРАТ",L5)))</formula>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>$L5="УКАЗАТЬ ВОЗВРАТ"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="7" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="В РАБОТЕ" dxfId="7">
-      <formula>NOT(ISERROR(SEARCH("В РАБОТЕ",L5)))</formula>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>$L5="ПРОВЕРИТЬ ОСНОВАНИЕ"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>$L5="ВОЗВРАТ ЗАФИКСИРОВАН"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>$L5="ПРОВЕРИТЬ"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>$L5="В РАБОТЕ"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B54" type="date">
-      <formula1>2000-1-1</formula1>
+    <dataValidation allowBlank="false" error="Исправьте значение по правилу поля." errorStyle="stop" errorTitle="Недопустимое значение" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B5:B54" type="date">
+      <formula1>DATE(2000,1,1)</formula1>
       <formula2>TODAY()</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G54" type="whole">
+    <dataValidation allowBlank="false" error="Исправьте значение по правилу поля." errorStyle="stop" errorTitle="Недопустимое значение" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5:G54" type="whole">
       <formula1>1</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H54" type="list">
+    <dataValidation allowBlank="false" error="Исправьте значение по правилу поля." errorStyle="stop" errorTitle="Недопустимое значение" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H5:H54" type="list">
       <formula1>"Подпись на экземпляре,ЭДО,Письмо / курьер,Иное подтверждение"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I5:I54" type="list">
+    <dataValidation allowBlank="false" error="Исправьте значение по правилу поля." errorStyle="stop" errorTitle="Недопустимое значение" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I5:I54" type="list">
       <formula1>"На проверке,Принято,Возврат"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J54" type="date">
-      <formula1>2000-1-1</formula1>
+    <dataValidation allowBlank="false" error="Исправьте значение по правилу поля." errorStyle="stop" errorTitle="Недопустимое значение" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J54" type="date">
+      <formula1>DATE(2000,1,1)</formula1>
       <formula2>TODAY()</formula2>
     </dataValidation>
   </dataValidations>
